--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F328"/>
+  <dimension ref="A1:F329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8308,6 +8308,30 @@
       <c r="F328" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>368.09</v>
+      </c>
+      <c r="C329" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="D329" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="E329" t="n">
+        <v>363.95</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11845,6 +11869,16 @@
       </c>
       <c r="B352" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -12013,28 +12047,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02739767871101362</v>
+        <v>0.02472582049356305</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00251216422127376</v>
+        <v>0.00205513061046092</v>
       </c>
       <c r="M2" t="n">
-        <v>2.980761260293842</v>
+        <v>2.982741177879099</v>
       </c>
       <c r="N2" t="n">
-        <v>15.39540429599683</v>
+        <v>15.39927450624858</v>
       </c>
       <c r="O2" t="n">
-        <v>3.923697783468655</v>
+        <v>3.924190936517816</v>
       </c>
       <c r="P2" t="n">
-        <v>371.4734426541637</v>
+        <v>371.5013237183675</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12095,28 +12129,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1553205371696284</v>
+        <v>0.1520288196784363</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07667329786736377</v>
+        <v>0.07383970149910257</v>
       </c>
       <c r="M3" t="n">
-        <v>2.479141966051866</v>
+        <v>2.483825152130037</v>
       </c>
       <c r="N3" t="n">
-        <v>15.00627837982212</v>
+        <v>15.0376436958183</v>
       </c>
       <c r="O3" t="n">
-        <v>3.873793796760757</v>
+        <v>3.877840081258934</v>
       </c>
       <c r="P3" t="n">
-        <v>367.399925335715</v>
+        <v>367.4342746833387</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12177,28 +12211,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08027945768513926</v>
+        <v>0.07703849480046177</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01743770906658082</v>
+        <v>0.01613221416331934</v>
       </c>
       <c r="M4" t="n">
-        <v>2.996633613692112</v>
+        <v>3.000999181221627</v>
       </c>
       <c r="N4" t="n">
-        <v>18.75786924984884</v>
+        <v>18.77543703232378</v>
       </c>
       <c r="O4" t="n">
-        <v>4.331035586305987</v>
+        <v>4.333063238901987</v>
       </c>
       <c r="P4" t="n">
-        <v>362.206624501752</v>
+        <v>362.2404442208073</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12259,28 +12293,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1400033492801471</v>
+        <v>0.1360023568534946</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05032624259313856</v>
+        <v>0.04768487580257463</v>
       </c>
       <c r="M5" t="n">
-        <v>3.107968884101806</v>
+        <v>3.11422472712234</v>
       </c>
       <c r="N5" t="n">
-        <v>19.10560349178855</v>
+        <v>19.16128409024938</v>
       </c>
       <c r="O5" t="n">
-        <v>4.370995709422345</v>
+        <v>4.377360402142983</v>
       </c>
       <c r="P5" t="n">
-        <v>366.4304559745074</v>
+        <v>366.4722066654677</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12322,7 +12356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F328"/>
+  <dimension ref="A1:F329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22821,6 +22855,38 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-35.4304183789917,174.3611082222829</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-35.43114370511485,174.36101835914707</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-35.4318771869837,174.36101856452242</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-35.43259664151357,174.36119337729875</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F329"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8330,6 +8330,30 @@
         <v>363.95</v>
       </c>
       <c r="F329" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="C330" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="D330" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="E330" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="F330" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8346,7 +8370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11879,6 +11903,16 @@
       </c>
       <c r="B353" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -12047,28 +12081,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02472582049356305</v>
+        <v>0.02178764433628735</v>
       </c>
       <c r="J2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00205513061046092</v>
+        <v>0.001601693584246222</v>
       </c>
       <c r="M2" t="n">
-        <v>2.982741177879099</v>
+        <v>2.986036350133266</v>
       </c>
       <c r="N2" t="n">
-        <v>15.39927450624858</v>
+        <v>15.41402205306095</v>
       </c>
       <c r="O2" t="n">
-        <v>3.924190936517816</v>
+        <v>3.926069542565561</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5013237183675</v>
+        <v>371.532091774767</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12129,28 +12163,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1520288196784363</v>
+        <v>0.1482765358343736</v>
       </c>
       <c r="J3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07383970149910257</v>
+        <v>0.07053319710988959</v>
       </c>
       <c r="M3" t="n">
-        <v>2.483825152130037</v>
+        <v>2.490036620275299</v>
       </c>
       <c r="N3" t="n">
-        <v>15.0376436958183</v>
+        <v>15.09232668547856</v>
       </c>
       <c r="O3" t="n">
-        <v>3.877840081258934</v>
+        <v>3.884884385085168</v>
       </c>
       <c r="P3" t="n">
-        <v>367.4342746833387</v>
+        <v>367.4735679301562</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12211,28 +12245,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07703849480046177</v>
+        <v>0.07403271785584772</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01613221416331934</v>
+        <v>0.0149729208400956</v>
       </c>
       <c r="M4" t="n">
-        <v>3.000999181221627</v>
+        <v>3.004237902996588</v>
       </c>
       <c r="N4" t="n">
-        <v>18.77543703232378</v>
+        <v>18.78278770067937</v>
       </c>
       <c r="O4" t="n">
-        <v>4.333063238901987</v>
+        <v>4.333911362808355</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2404442208073</v>
+        <v>362.2719201805884</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12293,28 +12327,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1360023568534946</v>
+        <v>0.1319577535571855</v>
       </c>
       <c r="J5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04768487580257463</v>
+        <v>0.04506787748467023</v>
       </c>
       <c r="M5" t="n">
-        <v>3.11422472712234</v>
+        <v>3.121260854916093</v>
       </c>
       <c r="N5" t="n">
-        <v>19.16128409024938</v>
+        <v>19.21968416058468</v>
       </c>
       <c r="O5" t="n">
-        <v>4.377360402142983</v>
+        <v>4.384026021887266</v>
       </c>
       <c r="P5" t="n">
-        <v>366.4722066654677</v>
+        <v>366.5145610294245</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12356,7 +12390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F329"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22887,6 +22921,38 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-35.43041808819696,174.3611031680247</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-35.43114379423967,174.36100998865993</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-35.43187684714829,174.36102195378052</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-35.432596813960195,174.36119196094452</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F330"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8356,6 +8356,30 @@
       <c r="F330" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>366.68</v>
+      </c>
+      <c r="C331" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="D331" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="E331" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11913,6 +11937,26 @@
       </c>
       <c r="B354" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -12081,28 +12125,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02178764433628735</v>
+        <v>0.01826691095519714</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001601693584246222</v>
+        <v>0.001128210693830067</v>
       </c>
       <c r="M2" t="n">
-        <v>2.986036350133266</v>
+        <v>2.991786658769998</v>
       </c>
       <c r="N2" t="n">
-        <v>15.41402205306095</v>
+        <v>15.45552479008191</v>
       </c>
       <c r="O2" t="n">
-        <v>3.926069542565561</v>
+        <v>3.931351522069976</v>
       </c>
       <c r="P2" t="n">
-        <v>371.532091774767</v>
+        <v>371.5691207636381</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12163,28 +12207,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1482765358343736</v>
+        <v>0.1450937985032285</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07053319710988959</v>
+        <v>0.06790153725885806</v>
       </c>
       <c r="M3" t="n">
-        <v>2.490036620275299</v>
+        <v>2.494174327424221</v>
       </c>
       <c r="N3" t="n">
-        <v>15.09232668547856</v>
+        <v>15.11868027824417</v>
       </c>
       <c r="O3" t="n">
-        <v>3.884884385085168</v>
+        <v>3.888274717434993</v>
       </c>
       <c r="P3" t="n">
-        <v>367.4735679301562</v>
+        <v>367.5070420767211</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12245,28 +12289,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07403271785584772</v>
+        <v>0.0720489260970483</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0149729208400956</v>
+        <v>0.01427427516818969</v>
       </c>
       <c r="M4" t="n">
-        <v>3.004237902996588</v>
+        <v>3.003166295580427</v>
       </c>
       <c r="N4" t="n">
-        <v>18.78278770067937</v>
+        <v>18.75387628818352</v>
       </c>
       <c r="O4" t="n">
-        <v>4.333911362808355</v>
+        <v>4.330574590996386</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2719201805884</v>
+        <v>362.2927845275889</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12327,28 +12371,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1319577535571855</v>
+        <v>0.1289408295598655</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04506787748467023</v>
+        <v>0.04328178505047875</v>
       </c>
       <c r="M5" t="n">
-        <v>3.121260854916093</v>
+        <v>3.124136192432771</v>
       </c>
       <c r="N5" t="n">
-        <v>19.21968416058468</v>
+        <v>19.22621503743998</v>
       </c>
       <c r="O5" t="n">
-        <v>4.384026021887266</v>
+        <v>4.384770807857576</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5145610294245</v>
+        <v>366.546291249532</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12390,7 +12434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F330"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22953,6 +22997,38 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-35.43041748764194,174.3610927298828</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-35.431143696905956,174.361019130113</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-35.431875169894695,174.36103868140867</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-35.432594784394915,174.36120863034387</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F331"/>
+  <dimension ref="A1:F332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8380,6 +8380,30 @@
       <c r="F331" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="C332" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="D332" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="E332" t="n">
+        <v>366.49</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11957,6 +11981,16 @@
       </c>
       <c r="B356" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -12125,28 +12159,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01826691095519714</v>
+        <v>0.01636815833426327</v>
       </c>
       <c r="J2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001128210693830067</v>
+        <v>0.0009113037703557536</v>
       </c>
       <c r="M2" t="n">
-        <v>2.991786658769998</v>
+        <v>2.990589106766294</v>
       </c>
       <c r="N2" t="n">
-        <v>15.45552479008191</v>
+        <v>15.43424810792826</v>
       </c>
       <c r="O2" t="n">
-        <v>3.931351522069976</v>
+        <v>3.928644563704924</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5691207636381</v>
+        <v>371.5892103320444</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12207,28 +12241,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1450937985032285</v>
+        <v>0.1417851464449962</v>
       </c>
       <c r="J3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06790153725885806</v>
+        <v>0.06518031601672059</v>
       </c>
       <c r="M3" t="n">
-        <v>2.494174327424221</v>
+        <v>2.498796864423739</v>
       </c>
       <c r="N3" t="n">
-        <v>15.11868027824417</v>
+        <v>15.15018105995912</v>
       </c>
       <c r="O3" t="n">
-        <v>3.888274717434993</v>
+        <v>3.892323349872043</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5070420767211</v>
+        <v>367.5420489497194</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12289,28 +12323,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0720489260970483</v>
+        <v>0.07034833497221231</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01427427516818969</v>
+        <v>0.01370282425773162</v>
       </c>
       <c r="M4" t="n">
-        <v>3.003166295580427</v>
+        <v>3.000874081037512</v>
       </c>
       <c r="N4" t="n">
-        <v>18.75387628818352</v>
+        <v>18.71760644466195</v>
       </c>
       <c r="O4" t="n">
-        <v>4.330574590996386</v>
+        <v>4.32638491637787</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2927845275889</v>
+        <v>362.3107774674573</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12371,28 +12405,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1289408295598655</v>
+        <v>0.1266738301217067</v>
       </c>
       <c r="J5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04328178505047875</v>
+        <v>0.04205888125335544</v>
       </c>
       <c r="M5" t="n">
-        <v>3.124136192432771</v>
+        <v>3.123794356125341</v>
       </c>
       <c r="N5" t="n">
-        <v>19.22621503743998</v>
+        <v>19.20436126981003</v>
       </c>
       <c r="O5" t="n">
-        <v>4.384770807857576</v>
+        <v>4.382278091336745</v>
       </c>
       <c r="P5" t="n">
-        <v>366.546291249532</v>
+        <v>366.5702770177609</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12434,7 +12468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F331"/>
+  <dimension ref="A1:F332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23029,6 +23063,38 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-35.43041904276151,174.36111975917674</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-35.43114372035993,174.3610169273532</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-35.43187470947176,174.36104327330645</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-35.432593272168305,174.36122105068003</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F332"/>
+  <dimension ref="A1:F334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8402,6 +8402,54 @@
         <v>366.49</v>
       </c>
       <c r="F332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="C333" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="D333" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="E333" t="n">
+        <v>365.87</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="C334" t="n">
+        <v>362.23</v>
+      </c>
+      <c r="D334" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="E334" t="n">
+        <v>366.42</v>
+      </c>
+      <c r="F334" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8418,7 +8466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11991,6 +12039,26 @@
       </c>
       <c r="B357" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -12159,28 +12227,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01636815833426327</v>
+        <v>0.01187183046103422</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009113037703557536</v>
+        <v>0.0004844467380344941</v>
       </c>
       <c r="M2" t="n">
-        <v>2.990589106766294</v>
+        <v>2.991115970886716</v>
       </c>
       <c r="N2" t="n">
-        <v>15.43424810792826</v>
+        <v>15.41398314157908</v>
       </c>
       <c r="O2" t="n">
-        <v>3.928644563704924</v>
+        <v>3.926064587036117</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5892103320444</v>
+        <v>371.6369249045492</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12241,28 +12309,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1417851464449962</v>
+        <v>0.1309696546361939</v>
       </c>
       <c r="J3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06518031601672059</v>
+        <v>0.05548108564088872</v>
       </c>
       <c r="M3" t="n">
-        <v>2.498796864423739</v>
+        <v>2.52591001699053</v>
       </c>
       <c r="N3" t="n">
-        <v>15.15018105995912</v>
+        <v>15.4790057125061</v>
       </c>
       <c r="O3" t="n">
-        <v>3.892323349872043</v>
+        <v>3.934336756367724</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5420489497194</v>
+        <v>367.6568224127298</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12323,28 +12391,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07034833497221231</v>
+        <v>0.06460341935970641</v>
       </c>
       <c r="J4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01370282425773162</v>
+        <v>0.01167672070221271</v>
       </c>
       <c r="M4" t="n">
-        <v>3.000874081037512</v>
+        <v>3.006163064029481</v>
       </c>
       <c r="N4" t="n">
-        <v>18.71760644466195</v>
+        <v>18.72514245077534</v>
       </c>
       <c r="O4" t="n">
-        <v>4.32638491637787</v>
+        <v>4.327255764427998</v>
       </c>
       <c r="P4" t="n">
-        <v>362.3107774674573</v>
+        <v>362.3717437366467</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12405,28 +12473,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1266738301217067</v>
+        <v>0.1218019881811912</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K5" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04205888125335544</v>
+        <v>0.03939785657552941</v>
       </c>
       <c r="M5" t="n">
-        <v>3.123794356125341</v>
+        <v>3.124612017806066</v>
       </c>
       <c r="N5" t="n">
-        <v>19.20436126981003</v>
+        <v>19.17413136992575</v>
       </c>
       <c r="O5" t="n">
-        <v>4.382278091336745</v>
+        <v>4.378827625052824</v>
       </c>
       <c r="P5" t="n">
-        <v>366.5702770177609</v>
+        <v>366.6219734250643</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12468,7 +12536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F332"/>
+  <dimension ref="A1:F334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23095,6 +23163,70 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-35.430418802540174,174.3611155839199</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-35.43114403932987,174.36098696982015</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-35.4318760907401,174.36102949761292</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-35.4325940946075,174.36121429576042</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-35.43041850542413,174.36111041978648</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-35.4311441952941,174.36097232146741</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-35.43187743911958,174.36101604991157</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-35.43259336502437,174.36122028802782</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0072/nzd0072.xlsx
+++ b/data/nzd0072/nzd0072.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F334"/>
+  <dimension ref="A1:F336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8450,6 +8450,54 @@
         <v>366.42</v>
       </c>
       <c r="F334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>368.82</v>
+      </c>
+      <c r="C335" t="n">
+        <v>365.66</v>
+      </c>
+      <c r="D335" t="n">
+        <v>360.07</v>
+      </c>
+      <c r="E335" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="C336" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="D336" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="E336" t="n">
+        <v>368</v>
+      </c>
+      <c r="F336" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8466,7 +8514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12059,6 +12107,26 @@
       </c>
       <c r="B359" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -12227,28 +12295,28 @@
         <v>0.1137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01187183046103422</v>
+        <v>0.007355064042428746</v>
       </c>
       <c r="J2" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004844467380344941</v>
+        <v>0.0001878101408849808</v>
       </c>
       <c r="M2" t="n">
-        <v>2.991115970886716</v>
+        <v>2.991673798031279</v>
       </c>
       <c r="N2" t="n">
-        <v>15.41398314157908</v>
+        <v>15.39724768529455</v>
       </c>
       <c r="O2" t="n">
-        <v>3.926064587036117</v>
+        <v>3.923932681035003</v>
       </c>
       <c r="P2" t="n">
-        <v>371.6369249045492</v>
+        <v>371.685019445494</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12309,28 +12377,28 @@
         <v>0.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1309696546361939</v>
+        <v>0.1232670497399044</v>
       </c>
       <c r="J3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05548108564088872</v>
+        <v>0.04948514442421081</v>
       </c>
       <c r="M3" t="n">
-        <v>2.52591001699053</v>
+        <v>2.541379383703114</v>
       </c>
       <c r="N3" t="n">
-        <v>15.4790057125061</v>
+        <v>15.60446416176544</v>
       </c>
       <c r="O3" t="n">
-        <v>3.934336756367724</v>
+        <v>3.950248620247267</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6568224127298</v>
+        <v>367.7388389671394</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12391,28 +12459,28 @@
         <v>0.1256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06460341935970641</v>
+        <v>0.05952358483830607</v>
       </c>
       <c r="J4" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K4" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01167672070221271</v>
+        <v>0.01002452048914937</v>
       </c>
       <c r="M4" t="n">
-        <v>3.006163064029481</v>
+        <v>3.00924258813765</v>
       </c>
       <c r="N4" t="n">
-        <v>18.72514245077534</v>
+        <v>18.70724257369505</v>
       </c>
       <c r="O4" t="n">
-        <v>4.327255764427998</v>
+        <v>4.325186998696709</v>
       </c>
       <c r="P4" t="n">
-        <v>362.3717437366467</v>
+        <v>362.4258309501129</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12473,28 +12541,28 @@
         <v>0.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1218019881811912</v>
+        <v>0.1197464456327866</v>
       </c>
       <c r="J5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03939785657552941</v>
+        <v>0.03863749356985602</v>
       </c>
       <c r="M5" t="n">
-        <v>3.124612017806066</v>
+        <v>3.114309076205331</v>
       </c>
       <c r="N5" t="n">
-        <v>19.17413136992575</v>
+        <v>19.07542783064012</v>
       </c>
       <c r="O5" t="n">
-        <v>4.378827625052824</v>
+        <v>4.367542539076194</v>
       </c>
       <c r="P5" t="n">
-        <v>366.6219734250643</v>
+        <v>366.6438612255914</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12536,7 +12604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F334"/>
+  <dimension ref="A1:F336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23227,6 +23295,70 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-35.430418840469876,174.36111624317098</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-35.43114379306696,174.36101009879792</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-35.43187637576353,174.36102665500943</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-35.43259059260577,174.3612430586429</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-35.430418303132235,174.36110690378075</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-35.43114392909844,174.36099732279118</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-35.43187633191378,174.36102709233305</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-35.43259126912937,174.3612375021772</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
